--- a/reports/Swiggy_GST_Return_Working.xlsx
+++ b/reports/Swiggy_GST_Return_Working.xlsx
@@ -957,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1141,111 +1141,140 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>₹6.02 higher than the amount discharged: ₹5.90 is the cancellation-compensation policy (on the 20% not compensated) and ₹0.12 is paise rounding on the other orders — both explained, nothing to recover</t>
-        </is>
+          <t>Fully accounted for: ₹2,305.92 discharged u/s 9(5) + ₹5.90 GST on the un-compensated 20% (deducted inside the ₹123.90 cancellation charge) + ₹0.12 paise rounding</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Complaint &amp; cancellation charges deducted (line C)</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="C15" s="11">
+        <f> un-compensated 20% of the cancelled order (₹118.00) + GST @5% on it (₹5.90) — the deduction is GST-inclusive</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        GST on the un-compensated 20% — not payable</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>₹118.00 × 5%; not a supply, so the tax is not payable and comes back through the cancellation deduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Memorandum items</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="21" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        GST charged by Swiggy on its own service fee @18%</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>2326.64</v>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Recovered from you in the payouts; this is Swiggy's output tax. ITC is not available to a 5% restaurant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Swiggy fees (commission + payment collection) excluding GST</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>12925.06</v>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Swiggy's consideration for the services it provides to you</t>
-        </is>
-      </c>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="21" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        TCS under Section 52</t>
+          <t xml:space="preserve">        GST charged by Swiggy on its own service fee @18%</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>0</v>
+        <v>2326.64</v>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Not applicable to Section 9(5) supplies — Circular 167/23/2021-GST</t>
+          <t>Recovered from you in the payouts; this is Swiggy's output tax. ITC is not available to a 5% restaurant.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        TDS under Section 194-O (income tax)</t>
+          <t xml:space="preserve">        Swiggy fees (commission + payment collection) excluding GST</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>46.14</v>
+        <v>12925.06</v>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Deducted at 0.1% of the supply value (on the 80% compensation value for the cancelled order); claim credit in Form 26AS / AIS — not a GST item</t>
+          <t>Swiggy's consideration for the services it provides to you</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">        TCS under Section 52</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Not applicable to Section 9(5) supplies — Circular 167/23/2021-GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        TDS under Section 194-O (income tax)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Deducted at 0.1% of the supply value (on the 80% compensation value for the cancelled order); claim credit in Form 26AS / AIS — not a GST item</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">        Gross amount collected from customers</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n">
+      <c r="B23" s="13" t="n">
         <v>48548.27</v>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Total customer paid across all orders</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">        Net payouts credited by Swiggy</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B24" s="10" t="n">
         <v>30139.91</v>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Settlement after commission, charges, ads, GST and TDS</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>All amounts in ₹. Prepared 05 October 2026 from 5 annexures. Confirm the reporting view with your CA before filing.</t>
         </is>
@@ -2576,16 +2605,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2624,20 +2654,30 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Cancellation adjustment</t>
+          <t>Cancellation adjustment (value)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
+          <t>GST on the un-compensated 20%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Complaint &amp; cancellation charges deducted</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
           <t>GST on reportable value</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
@@ -2655,13 +2695,19 @@
       <c r="C7" s="15" t="n">
         <v>-118</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="F7" s="13" t="n">
         <v>518.25</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>518.25</v>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>Agrees to the paisa</t>
         </is>
@@ -2680,12 +2726,18 @@
         <v>-0</v>
       </c>
       <c r="D8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13" t="n">
         <v>572.25</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>572.25</v>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>Agrees to the paisa</t>
         </is>
@@ -2704,12 +2756,18 @@
         <v>-0</v>
       </c>
       <c r="D9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13" t="n">
         <v>627.25</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>627.25</v>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>Agrees to the paisa</t>
         </is>
@@ -2728,12 +2786,18 @@
         <v>-0</v>
       </c>
       <c r="D10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13" t="n">
         <v>232.17</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>232.17</v>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>Agrees to the paisa</t>
         </is>
@@ -2752,12 +2816,18 @@
         <v>-0</v>
       </c>
       <c r="D11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13" t="n">
         <v>356</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="G11" s="13" t="n">
         <v>356</v>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Agrees to the paisa</t>
         </is>
@@ -2776,12 +2846,18 @@
         <v>-118</v>
       </c>
       <c r="D12" s="18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="F12" s="18" t="n">
         <v>2305.92</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="G12" s="18" t="n">
         <v>2305.92</v>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>GST discharged = 5% × reportable value</t>
         </is>
@@ -2838,7 +2914,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Order 247576408124202 — ₹118.00 × 5% = ₹5.90 of GST was collected but not required to be discharged, because the restaurant was compensated at 80% of the order value</t>
+          <t>Order 247576408124202 — ₹118.00 × 5% = ₹5.90. This GST is not payable (the 20% is not a supply) and is deducted from the payout inside the ₹123.90 'Complaint &amp; Cancellation Charges' amount</t>
         </is>
       </c>
     </row>
@@ -3422,8 +3498,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A42:G42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/Swiggy_GST_Return_Working.xlsx
+++ b/reports/Swiggy_GST_Return_Working.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>5% (CGST 2.5% + SGST 2.5%), intra-state — place of supply Gujarat</t>
+          <t>5% (CGST 2.50% + SGST 2.50%), intra-state — place of supply Gujarat (24)</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>•  Every figure is taken from the Swiggy annexures for the five payout cycles covering 01 Sep 2026 – 30 Sep 2026, so the whole month is represented by one GST return period.</t>
+          <t>•  Every figure is taken from the Swiggy annexures for the five payout cycle(s) covering 01 Sep – 30 Sep 2026, so the whole period is represented by one GST return period.</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>•  Where an order is cancelled before pickup and the cancellation is not on the restaurant, Swiggy compensates the restaurant at 80% of the order value; GST u/s 9(5) and TDS u/s 194-O are then computed on that 80% value, not on the full billed value. September 2026 has one such order (247576408124202), which reduces the GST-reportable value by ₹118.00 and fully explains the difference between the GST billed to customers and the GST discharged by Swiggy.</t>
+          <t>•  Where an order is cancelled before pickup and the cancellation is not on the restaurant, Swiggy compensates the restaurant at 80% of the order value; GST u/s 9(5) and TDS u/s 194-O are then computed on that 80% value, not on the full billed value. September 2026 has 1 such order(s) (order 247576408124202), which reduces the GST-reportable value by ₹118.00 and fully explains the difference between the GST billed to customers and the GST discharged by Swiggy.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>One order in the 01–05 Sep cycle — 247576408124202, cancelled by Swiggy before pickup (customer had paid ₹619.50)</t>
+          <t>1 order(s) cancelled before pickup by Swiggy — 247576408124202, cancelled in the 01 – 05 Sep cycle</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Swiggy's policy pays the restaurant 80% of the order value as compensation for a pre-pickup cancellation, so GST is discharged on ₹472.00 (80% × ₹590.00), not on ₹590.00 — ₹590.00 × 20% = ₹118.00</t>
+          <t>Swiggy's policy pays the restaurant 80% of the order value as compensation for a pre-pickup cancellation, so GST is discharged on ₹472.00 (80% × ₹590.00), not on ₹590.00 — the 20% not compensated is ₹118.00</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">        GST @5% on the reportable value</t>
+          <t xml:space="preserve">        GST 5% on the reportable value</t>
         </is>
       </c>
       <c r="B10" s="18" t="n">
@@ -1088,7 +1088,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        CGST @2.5%</t>
+          <t xml:space="preserve">        CGST @2.50%</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Intra-state supply — place of supply Gujarat</t>
+          <t>Intra-state supply — place of supply Gujarat (24)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SGST @2.5%</t>
+          <t xml:space="preserve">        SGST @2.50%</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Intra-state supply — place of supply Gujarat</t>
+          <t>Intra-state supply — place of supply Gujarat (24)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
         <v>123.9</v>
       </c>
       <c r="C15" s="11">
-        <f> un-compensated 20% of the cancelled order (₹118.00) + GST @5% on it (₹5.90) — the deduction is GST-inclusive</f>
+        <f> un-compensated 20% of the cancelled order (₹118.00) + GST 5% on it (₹5.90) — the deduction is GST-inclusive</f>
         <v/>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>CGST @2.5%</t>
+          <t>CGST @2.50%</t>
         </is>
       </c>
       <c r="H1" s="6" t="inlineStr">
         <is>
-          <t>SGST @2.5%</t>
+          <t>SGST @2.50%</t>
         </is>
       </c>
       <c r="I1" s="6" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B2" s="23" t="n">
@@ -1431,7 +1431,7 @@
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B3" s="25" t="n">
@@ -1477,7 +1477,7 @@
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B4" s="23" t="n">
@@ -1523,7 +1523,7 @@
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
@@ -1569,7 +1569,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B6" s="23" t="n">
@@ -1970,7 +1970,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
@@ -1992,7 +1992,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
@@ -2014,7 +2014,7 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
@@ -2058,7 +2058,7 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
@@ -2123,7 +2123,7 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>•  An order cancelled before pickup (not caused by the restaurant) is compensated at 80% of the order value; GST is discharged on that compensation value, so ₹118.00 of billed value is not reportable for GST. An order cancelled by the restaurant has no supply and no GST.</t>
+          <t>•  An order cancelled before pickup (not caused by the restaurant) is compensated at 80% of the order value; GST is discharged on that compensation value, so ₹118.00 of billed value is not reportable for GST (20% of the billed value). An order cancelled by the restaurant has no supply and no GST.</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
@@ -2716,7 +2716,7 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -2746,7 +2746,7 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
@@ -2776,7 +2776,7 @@
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
@@ -2806,7 +2806,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Each order's GST is rounded to the nearest paisa in the annexure (roughly ₹0.01 on 13 orders)</t>
+          <t>Each order's GST is rounded to the nearest paisa in the annexure (about ₹0.01 × 12 orders)</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
@@ -3028,7 +3028,7 @@
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
@@ -3059,7 +3059,7 @@
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -3090,7 +3090,7 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="34" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B29" s="34" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -3214,7 +3214,7 @@
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
@@ -3245,7 +3245,7 @@
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -3276,7 +3276,7 @@
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -3338,7 +3338,7 @@
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
@@ -3369,7 +3369,7 @@
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -3400,7 +3400,7 @@
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
@@ -3431,7 +3431,7 @@
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -3477,7 +3477,7 @@
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>•  On a pre-pickup cancellation the tax is discharged on the 80% compensation value, not on the full value the customer paid; that is the single reason the GST discharged is ₹5.90 lower than the GST billed this month. The remaining ₹0.12 is paise rounding inside the annexures.</t>
+          <t>•  On a pre-pickup cancellation the tax is discharged on the 80% compensation value, not on the full value the customer paid; that is the single reason the GST discharged is ₹5.90 lower than the GST billed in this period. The remaining ₹0.12 is paise rounding inside the annexures.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
@@ -3579,7 +3579,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
@@ -3594,7 +3594,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -3609,7 +3609,7 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
@@ -3624,7 +3624,7 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
@@ -3689,7 +3689,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
@@ -3703,14 +3703,14 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Compensated-cancellation effect included: TDS is deducted on the 80% compensation value (₹472.00), not on the billed ₹590.00</t>
+          <t>Compensated-cancellation effect included: TDS is deducted on the 80% compensation value, not on the billed value</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
@@ -3731,7 +3731,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
@@ -3752,7 +3752,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
@@ -3773,7 +3773,7 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
@@ -3976,7 +3976,7 @@
     <row r="2">
       <c r="A2" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B2" s="40" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="3">
       <c r="A3" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B3" s="40" t="inlineStr">
@@ -4104,7 +4104,7 @@
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B4" s="40" t="inlineStr">
@@ -4168,7 +4168,7 @@
     <row r="5">
       <c r="A5" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B5" s="40" t="inlineStr">
@@ -4232,7 +4232,7 @@
     <row r="6">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="7">
       <c r="A7" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B7" s="40" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="8">
       <c r="A8" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B8" s="40" t="inlineStr">
@@ -4424,7 +4424,7 @@
     <row r="9">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B9" s="40" t="inlineStr">
@@ -4488,7 +4488,7 @@
     <row r="10">
       <c r="A10" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B10" s="40" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="11">
       <c r="A11" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B11" s="40" t="inlineStr">
@@ -4616,7 +4616,7 @@
     <row r="12">
       <c r="A12" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B12" s="40" t="inlineStr">
@@ -4680,7 +4680,7 @@
     <row r="13">
       <c r="A13" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B13" s="40" t="inlineStr">
@@ -4744,7 +4744,7 @@
     <row r="14">
       <c r="A14" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B14" s="40" t="inlineStr">
@@ -4808,7 +4808,7 @@
     <row r="15">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B15" s="44" t="inlineStr">
@@ -4880,7 +4880,7 @@
     <row r="16">
       <c r="A16" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B16" s="40" t="inlineStr">
@@ -4944,7 +4944,7 @@
     <row r="17">
       <c r="A17" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B17" s="40" t="inlineStr">
@@ -5008,7 +5008,7 @@
     <row r="18">
       <c r="A18" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B18" s="40" t="inlineStr">
@@ -5072,7 +5072,7 @@
     <row r="19">
       <c r="A19" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B19" s="40" t="inlineStr">
@@ -5136,7 +5136,7 @@
     <row r="20">
       <c r="A20" s="40" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B20" s="40" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="21">
       <c r="A21" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B21" s="48" t="inlineStr">
@@ -5264,7 +5264,7 @@
     <row r="22">
       <c r="A22" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B22" s="48" t="inlineStr">
@@ -5328,7 +5328,7 @@
     <row r="23">
       <c r="A23" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B23" s="48" t="inlineStr">
@@ -5392,7 +5392,7 @@
     <row r="24">
       <c r="A24" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B24" s="48" t="inlineStr">
@@ -5456,7 +5456,7 @@
     <row r="25">
       <c r="A25" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B25" s="48" t="inlineStr">
@@ -5520,7 +5520,7 @@
     <row r="26">
       <c r="A26" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B26" s="48" t="inlineStr">
@@ -5584,7 +5584,7 @@
     <row r="27">
       <c r="A27" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B27" s="48" t="inlineStr">
@@ -5648,7 +5648,7 @@
     <row r="28">
       <c r="A28" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B28" s="48" t="inlineStr">
@@ -5712,7 +5712,7 @@
     <row r="29">
       <c r="A29" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B29" s="48" t="inlineStr">
@@ -5776,7 +5776,7 @@
     <row r="30">
       <c r="A30" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B30" s="48" t="inlineStr">
@@ -5840,7 +5840,7 @@
     <row r="31">
       <c r="A31" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B31" s="48" t="inlineStr">
@@ -5904,7 +5904,7 @@
     <row r="32">
       <c r="A32" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B32" s="48" t="inlineStr">
@@ -5968,7 +5968,7 @@
     <row r="33">
       <c r="A33" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B33" s="48" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="34">
       <c r="A34" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B34" s="48" t="inlineStr">
@@ -6096,7 +6096,7 @@
     <row r="35">
       <c r="A35" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B35" s="48" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="36">
       <c r="A36" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B36" s="48" t="inlineStr">
@@ -6224,7 +6224,7 @@
     <row r="37">
       <c r="A37" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B37" s="48" t="inlineStr">
@@ -6288,7 +6288,7 @@
     <row r="38">
       <c r="A38" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B38" s="48" t="inlineStr">
@@ -6352,7 +6352,7 @@
     <row r="39">
       <c r="A39" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B39" s="48" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="40">
       <c r="A40" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B40" s="48" t="inlineStr">
@@ -6480,7 +6480,7 @@
     <row r="41">
       <c r="A41" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B41" s="48" t="inlineStr">
@@ -6544,7 +6544,7 @@
     <row r="42">
       <c r="A42" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B42" s="48" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="43">
       <c r="A43" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B43" s="48" t="inlineStr">
@@ -6672,7 +6672,7 @@
     <row r="44">
       <c r="A44" s="48" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B44" s="48" t="inlineStr">
@@ -6736,7 +6736,7 @@
     <row r="45">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B45" s="44" t="inlineStr">
@@ -6808,7 +6808,7 @@
     <row r="46">
       <c r="A46" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B46" s="40" t="inlineStr">
@@ -6872,7 +6872,7 @@
     <row r="47">
       <c r="A47" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B47" s="40" t="inlineStr">
@@ -6936,7 +6936,7 @@
     <row r="48">
       <c r="A48" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B48" s="40" t="inlineStr">
@@ -7000,7 +7000,7 @@
     <row r="49">
       <c r="A49" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B49" s="40" t="inlineStr">
@@ -7064,7 +7064,7 @@
     <row r="50">
       <c r="A50" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B50" s="40" t="inlineStr">
@@ -7128,7 +7128,7 @@
     <row r="51">
       <c r="A51" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B51" s="40" t="inlineStr">
@@ -7192,7 +7192,7 @@
     <row r="52">
       <c r="A52" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B52" s="40" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="53">
       <c r="A53" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B53" s="40" t="inlineStr">
@@ -7320,7 +7320,7 @@
     <row r="54">
       <c r="A54" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B54" s="40" t="inlineStr">
@@ -7384,7 +7384,7 @@
     <row r="55">
       <c r="A55" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B55" s="40" t="inlineStr">
@@ -7448,7 +7448,7 @@
     <row r="56">
       <c r="A56" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B56" s="40" t="inlineStr">
@@ -7512,7 +7512,7 @@
     <row r="57">
       <c r="A57" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B57" s="40" t="inlineStr">
@@ -7576,7 +7576,7 @@
     <row r="58">
       <c r="A58" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B58" s="40" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="59">
       <c r="A59" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B59" s="40" t="inlineStr">
@@ -7704,7 +7704,7 @@
     <row r="60">
       <c r="A60" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B60" s="40" t="inlineStr">
@@ -7768,7 +7768,7 @@
     <row r="61">
       <c r="A61" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B61" s="40" t="inlineStr">
@@ -7832,7 +7832,7 @@
     <row r="62">
       <c r="A62" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B62" s="40" t="inlineStr">
@@ -7896,7 +7896,7 @@
     <row r="63">
       <c r="A63" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B63" s="40" t="inlineStr">
@@ -7960,7 +7960,7 @@
     <row r="64">
       <c r="A64" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B64" s="40" t="inlineStr">
@@ -8024,7 +8024,7 @@
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B65" s="44" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="66">
       <c r="A66" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B66" s="40" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="67">
       <c r="A67" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B67" s="40" t="inlineStr">
@@ -8224,7 +8224,7 @@
     <row r="68">
       <c r="A68" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B68" s="40" t="inlineStr">
@@ -8288,7 +8288,7 @@
     <row r="69">
       <c r="A69" s="40" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B69" s="40" t="inlineStr">
@@ -8352,7 +8352,7 @@
     <row r="70">
       <c r="A70" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B70" s="48" t="inlineStr">
@@ -8416,7 +8416,7 @@
     <row r="71">
       <c r="A71" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B71" s="48" t="inlineStr">
@@ -8480,7 +8480,7 @@
     <row r="72">
       <c r="A72" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B72" s="48" t="inlineStr">
@@ -8544,7 +8544,7 @@
     <row r="73">
       <c r="A73" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B73" s="48" t="inlineStr">
@@ -8608,7 +8608,7 @@
     <row r="74">
       <c r="A74" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B74" s="48" t="inlineStr">
@@ -8672,7 +8672,7 @@
     <row r="75">
       <c r="A75" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B75" s="48" t="inlineStr">
@@ -8736,7 +8736,7 @@
     <row r="76">
       <c r="A76" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B76" s="48" t="inlineStr">
@@ -8800,7 +8800,7 @@
     <row r="77">
       <c r="A77" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B77" s="48" t="inlineStr">
@@ -8864,7 +8864,7 @@
     <row r="78">
       <c r="A78" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B78" s="48" t="inlineStr">
@@ -8928,7 +8928,7 @@
     <row r="79">
       <c r="A79" s="48" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B79" s="48" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="80">
       <c r="A80" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B80" s="40" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="81">
       <c r="A81" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B81" s="40" t="inlineStr">
@@ -9120,7 +9120,7 @@
     <row r="82">
       <c r="A82" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B82" s="40" t="inlineStr">
@@ -9184,7 +9184,7 @@
     <row r="83">
       <c r="A83" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B83" s="40" t="inlineStr">
@@ -9248,7 +9248,7 @@
     <row r="84">
       <c r="A84" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B84" s="40" t="inlineStr">
@@ -9312,7 +9312,7 @@
     <row r="85">
       <c r="A85" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B85" s="40" t="inlineStr">
@@ -9376,7 +9376,7 @@
     <row r="86">
       <c r="A86" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B86" s="40" t="inlineStr">
@@ -9440,7 +9440,7 @@
     <row r="87">
       <c r="A87" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B87" s="40" t="inlineStr">
@@ -9504,7 +9504,7 @@
     <row r="88">
       <c r="A88" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B88" s="40" t="inlineStr">
@@ -9568,7 +9568,7 @@
     <row r="89">
       <c r="A89" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B89" s="40" t="inlineStr">
@@ -9632,7 +9632,7 @@
     <row r="90">
       <c r="A90" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B90" s="40" t="inlineStr">
@@ -9696,7 +9696,7 @@
     <row r="91">
       <c r="A91" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B91" s="40" t="inlineStr">
@@ -9760,7 +9760,7 @@
     <row r="92">
       <c r="A92" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B92" s="40" t="inlineStr">
@@ -9824,7 +9824,7 @@
     <row r="93">
       <c r="A93" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B93" s="40" t="inlineStr">
@@ -9888,7 +9888,7 @@
     <row r="94">
       <c r="A94" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B94" s="40" t="inlineStr">
@@ -9952,7 +9952,7 @@
     <row r="95">
       <c r="A95" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B95" s="40" t="inlineStr">
@@ -10016,7 +10016,7 @@
     <row r="96">
       <c r="A96" s="40" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B96" s="40" t="inlineStr">
@@ -10138,7 +10138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -10226,14 +10226,14 @@
       </c>
       <c r="B6" s="43" t="inlineStr">
         <is>
-          <t>Cancellation adjustment = 20% of the compensated cancellation (₹590.00 × 20%)</t>
+          <t>Compensation + un-compensated value = net bill value (order 247576408124202)</t>
         </is>
       </c>
       <c r="C6" s="42" t="n">
-        <v>118</v>
+        <v>590</v>
       </c>
       <c r="D6" s="42" t="n">
-        <v>118</v>
+        <v>590</v>
       </c>
       <c r="E6" s="42" t="n">
         <v>0</v>
@@ -10250,14 +10250,14 @@
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>Compensated-cancellation value = 80% of the order value (₹590.00 × 80%)</t>
+          <t>GST discharged = 5% of the compensation-adjusted reportable value</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
-        <v>472</v>
+        <v>2305.92</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>472</v>
+        <v>2305.92</v>
       </c>
       <c r="E7" s="42" t="n">
         <v>0</v>
@@ -10274,17 +10274,17 @@
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>GST discharged = 5% of the compensation-adjusted reportable value</t>
+          <t>GST billed = GST discharged + GST on the un-compensated 20% + rounding</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
-        <v>2305.92</v>
+        <v>2311.94</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>2305.92</v>
+        <v>2311.94</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8" s="52" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>GST at 5% of the billed value (memo — tax effectively charged to customers)</t>
+          <t>GST at 5% of the billed value (memo — tax charged to customers)</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="B12" s="43" t="inlineStr">
         <is>
-          <t>GST discharged by Swiggy = payout breakup line 18</t>
+          <t>Order-wise register CGST + SGST = tax on the reportable value</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
@@ -10394,14 +10394,14 @@
       </c>
       <c r="B13" s="43" t="inlineStr">
         <is>
-          <t>Order count agrees with the annexures</t>
+          <t>GST discharged by Swiggy = payout breakup line 18</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>95</v>
+        <v>2305.92</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>95</v>
+        <v>2305.92</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>0</v>
@@ -10418,14 +10418,14 @@
       </c>
       <c r="B14" s="43" t="inlineStr">
         <is>
-          <t>TCS under Section 52 is nil</t>
+          <t>Order count agrees with the annexures</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>0</v>
@@ -10442,17 +10442,17 @@
       </c>
       <c r="B15" s="43" t="inlineStr">
         <is>
-          <t>TDS under Section 194-O = 0.1% of the reportable value</t>
+          <t>TCS under Section 52 is nil</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>46.12</v>
+        <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>46.14</v>
+        <v>0</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F15" s="52" t="inlineStr">
         <is>
@@ -10466,17 +10466,17 @@
       </c>
       <c r="B16" s="43" t="inlineStr">
         <is>
-          <t>Net payouts agree with the bank settlements</t>
+          <t>TDS under Section 194-O = 0.1% of the reportable value</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>30139.91</v>
+        <v>46.12</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>30139.91</v>
+        <v>46.14</v>
       </c>
       <c r="E16" s="42" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F16" s="52" t="inlineStr">
         <is>
@@ -10490,83 +10490,107 @@
       </c>
       <c r="B17" s="43" t="inlineStr">
         <is>
-          <t>GST collected vs GST discharged — explained by the cancellation policy + rounding</t>
+          <t>Net payouts agree with the bank settlements</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>30139.91</v>
       </c>
       <c r="D17" s="42" t="n">
+        <v>30139.91</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>GST billed vs GST discharged — explained by the cancellation policy + rounding</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="42" t="n">
         <v>6.02</v>
       </c>
-      <c r="E17" s="42" t="n">
+      <c r="E18" s="42" t="n">
         <v>6.02</v>
       </c>
-      <c r="F17" s="53" t="inlineStr">
+      <c r="F18" s="53" t="inlineStr">
         <is>
           <t>EXPLAINED</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Points to confirm with your CA before filing</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>•  Reporting view for Section 9(5) supplies: the working shows the full supply value in GSTR-1 Table 14 and GSTR-3B Table 3.1.1(ii) with nil tax payable by you. Confirm this is the treatment you file.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>•  The annexures do not contain your direct (dine-in / takeaway / own-delivery) sales — add them from your POS to complete GSTR-1 Table 7 and GSTR-3B Table 3.1(a).</t>
+          <t>•  Reporting view for Section 9(5) supplies: the working shows the full supply value in GSTR-1 Table 14 and GSTR-3B Table 3.1.1(ii) with nil tax payable by you. Confirm this is the treatment you file.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>•  GST billed to customers exceeded the GST discharged by ₹6.02. This is fully explained: ₹5.90 is the cancellation-compensation policy (order 247576408124202 was cancelled before pickup and compensated at 80%, so tax was discharged on ₹472.00 rather than ₹590.00) and ₹0.12 is paise rounding. No credit note is required — confirm that the customer's invoice for that order is also adjusted, or keep this working as the explanation for the difference.</t>
+          <t>•  The annexures do not contain your direct (dine-in / takeaway / own-delivery) sales — add them from your POS to complete GSTR-1 Table 7 and GSTR-3B Table 3.1(a).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>•  ITC of ₹-2,326.64 charged by Swiggy on its service fee is not claimable at the 5% restaurant rate; keep the annexures as evidence if the department asks why no ITC was taken.</t>
+          <t>•  GST billed to customers exceeded the GST discharged by ₹6.02. This is fully explained: ₹5.90 is the cancellation-compensation policy (order 247576408124202 was cancelled before pickup and compensated at 80%, so tax was discharged on ₹472.00 rather than ₹590.00) and ₹0.12 is paise rounding. No credit note is required — confirm that the customer's invoice for that order is also adjusted, or keep this working as the explanation for the difference.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>•  TDS of ₹46.14 under Section 194-O must be reconciled with Form 26AS / AIS and claimed in the income-tax return.</t>
+          <t>•  ITC of ₹2,326.64 charged by Swiggy on its service fee is not claimable at the 5% restaurant rate; keep the annexures as evidence if the department asks why no ITC was taken.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>•  Cess or state-specific levies on food delivery, if any, are not reflected in these annexures.</t>
+          <t>•  TDS of ₹46.14 under Section 194-O must be reconciled with Form 26AS / AIS and claimed in the income-tax return.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
+          <t>•  Cess or state-specific levies on food delivery, if any, are not reflected in these annexures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>•  This is a data-preparation workbook, not tax advice — the treatment finally adopted is the responsibility of the taxpayer and their CA.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>Source: Swiggy weekly payout annexures · Prepared 05 October 2026</t>
         </is>
@@ -10576,11 +10600,11 @@
   <mergeCells count="7">
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B20:F20"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
